--- a/ig/main/StructureDefinition-AS-PractitionerRole.xlsx
+++ b/ig/main/StructureDefinition-AS-PractitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-30T13:53:55+00:00</t>
+    <t>2023-04-12T09:48:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-AS-PractitionerRole.xlsx
+++ b/ig/main/StructureDefinition-AS-PractitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T09:48:34+00:00</t>
+    <t>2023-04-12T13:29:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-AS-PractitionerRole.xlsx
+++ b/ig/main/StructureDefinition-AS-PractitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T13:29:32+00:00</t>
+    <t>2023-05-02T09:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
